--- a/Cleaned/YSI_2026.xlsx
+++ b/Cleaned/YSI_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abec011338e80545/Desktop/Cleaned/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annab\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F900176-1563-4C57-A991-0BA341AFCE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4AB182-0EB4-4B0B-8C71-9931E6823E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{5C7CAE29-CC6A-4546-8536-9726002ADA2D}"/>
+    <workbookView xWindow="11910" yWindow="0" windowWidth="12180" windowHeight="15370" xr2:uid="{5C7CAE29-CC6A-4546-8536-9726002ADA2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
   <si>
     <t>DateTime</t>
   </si>
@@ -62,9 +62,6 @@
     <t>DUML</t>
   </si>
   <si>
-    <t>*pullout time used</t>
-  </si>
-  <si>
     <t>*redeploy time used</t>
   </si>
   <si>
@@ -74,9 +71,6 @@
     <t>*estimate</t>
   </si>
   <si>
-    <t>Moyst</t>
-  </si>
-  <si>
     <t>2026-04-24 13:45:00</t>
   </si>
   <si>
@@ -123,6 +117,105 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>pullout time used generally -- if redeploy was used, will be indicated</t>
+  </si>
+  <si>
+    <t>2026-07-03 14:06:00</t>
+  </si>
+  <si>
+    <t>2026-07-11 09:42:00</t>
+  </si>
+  <si>
+    <t>2026-07-17 13:34:00</t>
+  </si>
+  <si>
+    <t>2026-07-21 06:51:00</t>
+  </si>
+  <si>
+    <t>2026-08-07 09:53:00</t>
+  </si>
+  <si>
+    <t>2026-08-12 15:36:00</t>
+  </si>
+  <si>
+    <t>2026-08-21 10:36:00</t>
+  </si>
+  <si>
+    <t>2026-08-26 07:25:00</t>
+  </si>
+  <si>
+    <t>2026-09-04 13:32:00</t>
+  </si>
+  <si>
+    <t>2026-09-11 13:47:00</t>
+  </si>
+  <si>
+    <t>2026-09-19 09:42:00</t>
+  </si>
+  <si>
+    <t>7/31 excluded, YSI broken</t>
+  </si>
+  <si>
+    <t>*redploy time used</t>
+  </si>
+  <si>
+    <t>2026-07-03 13:30:00</t>
+  </si>
+  <si>
+    <t>2026-07-11 11:09:00</t>
+  </si>
+  <si>
+    <t>2026-07-17 14:28:00</t>
+  </si>
+  <si>
+    <t>2026-07-21 07:42:00</t>
+  </si>
+  <si>
+    <t>2026-08-07 11:10:00</t>
+  </si>
+  <si>
+    <t>2026-08-14 10:15:00</t>
+  </si>
+  <si>
+    <t>2026-08-21 11:42:00</t>
+  </si>
+  <si>
+    <t>2026-08-26 08:46:00</t>
+  </si>
+  <si>
+    <t>2026-09-09 14:25:00</t>
+  </si>
+  <si>
+    <t>2026-09-19 10:55:00</t>
+  </si>
+  <si>
+    <t>MOF</t>
+  </si>
+  <si>
+    <t>2026-07-09 14:04:00</t>
+  </si>
+  <si>
+    <t>2026-07-16 14:01:00</t>
+  </si>
+  <si>
+    <t>2026-07-29 08:54:00</t>
+  </si>
+  <si>
+    <t>2026-08-06 07:12:00</t>
+  </si>
+  <si>
+    <t>2026-08-14 09:03:00</t>
+  </si>
+  <si>
+    <t>2026-08-18 14:00:00</t>
+  </si>
+  <si>
+    <t>2026-08-25 09:51:00</t>
+  </si>
+  <si>
+    <t>2026-09-01 14:12:00</t>
   </si>
 </sst>
 </file>
@@ -132,7 +225,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,6 +238,24 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -167,26 +278,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,415 +647,1006 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CEC121-C9FF-4E93-8C41-37A7B71DADC1}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9">
+        <v>21.9</v>
+      </c>
+      <c r="C2" s="9">
+        <v>8.25</v>
+      </c>
+      <c r="D2" s="9">
+        <v>36.31</v>
+      </c>
+      <c r="E2" s="9">
+        <v>7.99</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="9">
+        <v>18.2</v>
+      </c>
+      <c r="C3" s="9">
+        <v>7.81</v>
+      </c>
+      <c r="D3" s="9">
+        <v>35.090000000000003</v>
+      </c>
+      <c r="E3" s="9">
+        <v>7.93</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="9">
+        <v>20.9</v>
+      </c>
+      <c r="C4" s="9">
+        <v>8.07</v>
+      </c>
+      <c r="D4" s="9">
+        <v>34.54</v>
+      </c>
+      <c r="E4" s="9">
+        <v>8.07</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="9">
+        <v>25.7</v>
+      </c>
+      <c r="C5" s="9">
+        <v>6.23</v>
+      </c>
+      <c r="D5" s="9">
+        <v>35.450000000000003</v>
+      </c>
+      <c r="E5" s="9">
+        <v>7.99</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="9">
+        <v>20.6</v>
+      </c>
+      <c r="C6" s="9">
+        <v>6.92</v>
+      </c>
+      <c r="D6" s="9">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="E6" s="9">
+        <v>7.95</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="9">
+        <v>26.3</v>
+      </c>
+      <c r="C7" s="9">
+        <v>4.75</v>
+      </c>
+      <c r="D7" s="9">
+        <v>36.86</v>
+      </c>
+      <c r="E7" s="9">
+        <v>7.76</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="9">
+        <v>28.3</v>
+      </c>
+      <c r="C8" s="9">
+        <v>5.48</v>
+      </c>
+      <c r="D8" s="9">
+        <v>37.06</v>
+      </c>
+      <c r="E8" s="9">
+        <v>7.92</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="9">
+        <v>32.1</v>
+      </c>
+      <c r="C9" s="9">
+        <v>6.1</v>
+      </c>
+      <c r="D9" s="9">
+        <v>37.42</v>
+      </c>
+      <c r="E9" s="9">
+        <v>7.85</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="5">
-        <v>21.9</v>
-      </c>
-      <c r="C2" s="5">
-        <v>8.25</v>
-      </c>
-      <c r="D2" s="5">
-        <v>36.31</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="B10" s="13">
+        <v>31.4</v>
+      </c>
+      <c r="C10" s="13">
+        <v>5.97</v>
+      </c>
+      <c r="D10" s="13">
+        <v>37.51</v>
+      </c>
+      <c r="E10" s="13">
+        <v>7.85</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="13">
+        <v>28.8</v>
+      </c>
+      <c r="C11" s="13">
+        <v>5.23</v>
+      </c>
+      <c r="D11" s="13">
+        <v>38.130000000000003</v>
+      </c>
+      <c r="E11" s="13">
+        <v>7.87</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="13">
+        <v>31.8</v>
+      </c>
+      <c r="C12" s="13">
+        <v>5.62</v>
+      </c>
+      <c r="D12" s="13">
+        <v>36.83</v>
+      </c>
+      <c r="E12" s="13">
+        <v>7.9</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="13">
+        <v>28.3</v>
+      </c>
+      <c r="C13" s="13">
+        <v>2.78</v>
+      </c>
+      <c r="D13" s="13">
+        <v>37.770000000000003</v>
+      </c>
+      <c r="E13" s="13">
+        <v>7.5</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="13">
+        <v>29.7</v>
+      </c>
+      <c r="C14" s="13">
+        <v>3.64</v>
+      </c>
+      <c r="D14" s="13">
+        <v>36.909999999999997</v>
+      </c>
+      <c r="E14" s="13">
+        <v>7.61</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="13">
+        <v>32.1</v>
+      </c>
+      <c r="C15" s="13">
+        <v>5.92</v>
+      </c>
+      <c r="D15" s="13">
+        <v>37.03</v>
+      </c>
+      <c r="E15" s="13">
+        <v>7.94</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="13">
+        <v>31.4</v>
+      </c>
+      <c r="C16" s="13">
+        <v>3.08</v>
+      </c>
+      <c r="D16" s="13">
+        <v>37.17</v>
+      </c>
+      <c r="E16" s="13">
+        <v>7.69</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="13">
+        <v>27.9</v>
+      </c>
+      <c r="C17" s="13">
+        <v>4.08</v>
+      </c>
+      <c r="D17" s="13">
+        <v>35.909999999999997</v>
+      </c>
+      <c r="E17" s="13">
+        <v>7.93</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="13">
+        <v>30.9</v>
+      </c>
+      <c r="C18" s="13">
+        <v>5.25</v>
+      </c>
+      <c r="D18" s="13">
+        <v>36.03</v>
+      </c>
+      <c r="E18" s="13">
         <v>7.99</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="F18" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="13">
+        <v>30.5</v>
+      </c>
+      <c r="C19" s="13">
+        <v>5.04</v>
+      </c>
+      <c r="D19" s="13">
+        <v>36.43</v>
+      </c>
+      <c r="E19" s="13">
+        <v>7.76</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="13">
+        <v>27</v>
+      </c>
+      <c r="C20" s="13">
+        <v>3.24</v>
+      </c>
+      <c r="D20" s="13">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="E20" s="13">
+        <v>7.63</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="9">
+        <v>25.4</v>
+      </c>
+      <c r="C22" s="9">
+        <v>6.41</v>
+      </c>
+      <c r="D22" s="9">
+        <v>35.130000000000003</v>
+      </c>
+      <c r="E22" s="9">
+        <v>7.99</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="9">
+        <v>25.9</v>
+      </c>
+      <c r="C23" s="9">
+        <v>6.15</v>
+      </c>
+      <c r="D23" s="9">
+        <v>35.94</v>
+      </c>
+      <c r="E23" s="9">
+        <v>7.99</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9">
+        <v>26.4</v>
+      </c>
+      <c r="C24" s="9">
+        <v>5.5</v>
+      </c>
+      <c r="D24" s="9">
+        <v>36.729999999999997</v>
+      </c>
+      <c r="E24" s="9">
+        <v>7.99</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="9">
+        <v>29.1</v>
+      </c>
+      <c r="C25" s="9">
+        <v>6.25</v>
+      </c>
+      <c r="D25" s="9">
+        <v>37.369999999999997</v>
+      </c>
+      <c r="E25" s="9">
+        <v>7.83</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="13">
+        <v>29.5</v>
+      </c>
+      <c r="C26" s="13">
+        <v>6.16</v>
+      </c>
+      <c r="D26" s="13">
+        <v>36.909999999999997</v>
+      </c>
+      <c r="E26" s="13">
+        <v>7.96</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="13">
+        <v>29.6</v>
+      </c>
+      <c r="C27" s="13">
+        <v>5.4</v>
+      </c>
+      <c r="D27" s="13">
+        <v>36.58</v>
+      </c>
+      <c r="E27" s="13">
+        <v>7.9</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="13">
+        <v>30.7</v>
+      </c>
+      <c r="C28" s="13">
+        <v>6.32</v>
+      </c>
+      <c r="D28" s="13">
+        <v>36.42</v>
+      </c>
+      <c r="E28" s="13">
+        <v>8.02</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="13">
+        <v>29.1</v>
+      </c>
+      <c r="C29" s="13">
+        <v>5.43</v>
+      </c>
+      <c r="D29" s="13">
+        <v>37.119999999999997</v>
+      </c>
+      <c r="E29" s="13">
+        <v>7.93</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="13">
+        <v>30.4</v>
+      </c>
+      <c r="C30" s="13">
+        <v>5.5</v>
+      </c>
+      <c r="D30" s="13">
+        <v>36.020000000000003</v>
+      </c>
+      <c r="E30" s="13">
+        <v>7.89</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="13">
+        <v>28.9</v>
+      </c>
+      <c r="C31" s="13">
+        <v>5.95</v>
+      </c>
+      <c r="D31" s="13">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="E31" s="13">
+        <v>7.78</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="13">
+        <v>31.7</v>
+      </c>
+      <c r="C32" s="13">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="D32" s="13">
+        <v>37.049999999999997</v>
+      </c>
+      <c r="E32" s="13">
+        <v>7.93</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="13">
+        <v>28.4</v>
+      </c>
+      <c r="C33" s="13">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="D33" s="13">
+        <v>36.4</v>
+      </c>
+      <c r="E33" s="13">
+        <v>8.01</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="13">
+        <v>28.3</v>
+      </c>
+      <c r="C34" s="13">
+        <v>6.31</v>
+      </c>
+      <c r="D34" s="13">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="E34" s="13">
+        <v>7.97</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="13">
+        <v>27.7</v>
+      </c>
+      <c r="C35" s="13">
+        <v>5.99</v>
+      </c>
+      <c r="D35" s="13">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="E35" s="13">
+        <v>7.96</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="9">
+        <v>21.8</v>
+      </c>
+      <c r="C37" s="9">
+        <v>7.33</v>
+      </c>
+      <c r="D37" s="9">
+        <v>31.9</v>
+      </c>
+      <c r="E37" s="9">
+        <v>7.86</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H37" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="5">
-        <v>18.2</v>
-      </c>
-      <c r="C3" s="5">
-        <v>7.81</v>
-      </c>
-      <c r="D3" s="5">
-        <v>35.090000000000003</v>
-      </c>
-      <c r="E3" s="5">
-        <v>7.93</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="5">
-        <v>20.9</v>
-      </c>
-      <c r="C4" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="D4" s="5">
-        <v>34.54</v>
-      </c>
-      <c r="E4" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="5">
-        <v>25.7</v>
-      </c>
-      <c r="C5" s="5">
-        <v>6.23</v>
-      </c>
-      <c r="D5" s="5">
-        <v>35.450000000000003</v>
-      </c>
-      <c r="E5" s="5">
-        <v>7.99</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="5">
-        <v>20.6</v>
-      </c>
-      <c r="C6" s="5">
-        <v>6.92</v>
-      </c>
-      <c r="D6" s="5">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="E6" s="5">
-        <v>7.95</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="5">
-        <v>26.3</v>
-      </c>
-      <c r="C7" s="5">
-        <v>4.75</v>
-      </c>
-      <c r="D7" s="5">
-        <v>36.86</v>
-      </c>
-      <c r="E7" s="5">
-        <v>7.76</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="5">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="9">
+        <v>29.8</v>
+      </c>
+      <c r="C38" s="9">
+        <v>4.92</v>
+      </c>
+      <c r="D38" s="9">
+        <v>37.54</v>
+      </c>
+      <c r="E38" s="9">
+        <v>7.78</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="9">
+        <v>27.6</v>
+      </c>
+      <c r="C39" s="9">
+        <v>5.41</v>
+      </c>
+      <c r="D39" s="9">
+        <v>34.08</v>
+      </c>
+      <c r="E39" s="9">
+        <v>7.85</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="13">
+        <v>32.4</v>
+      </c>
+      <c r="C40" s="13">
+        <v>6.09</v>
+      </c>
+      <c r="D40" s="13">
+        <v>34.64</v>
+      </c>
+      <c r="E40" s="13">
+        <v>7.85</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="13">
+        <v>30.7</v>
+      </c>
+      <c r="C41" s="13">
+        <v>5.76</v>
+      </c>
+      <c r="D41" s="13">
+        <v>35.49</v>
+      </c>
+      <c r="E41" s="13">
+        <v>7.89</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="13">
+        <v>27.8</v>
+      </c>
+      <c r="C42" s="13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D42" s="13">
+        <v>35.18</v>
+      </c>
+      <c r="E42" s="13">
+        <v>7.73</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="13">
         <v>28.3</v>
       </c>
-      <c r="C8" s="5">
-        <v>5.48</v>
-      </c>
-      <c r="D8" s="5">
-        <v>37.06</v>
-      </c>
-      <c r="E8" s="5">
-        <v>7.92</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="5">
-        <v>32.1</v>
-      </c>
-      <c r="C9" s="5">
-        <v>6.1</v>
-      </c>
-      <c r="D9" s="5">
-        <v>37.42</v>
-      </c>
-      <c r="E9" s="5">
-        <v>7.85</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="5">
-        <v>25.4</v>
-      </c>
-      <c r="C11" s="5">
-        <v>6.41</v>
-      </c>
-      <c r="D11" s="5">
-        <v>35.130000000000003</v>
-      </c>
-      <c r="E11" s="5">
-        <v>7.99</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="5">
-        <v>25.9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>6.15</v>
-      </c>
-      <c r="D12" s="5">
-        <v>35.94</v>
-      </c>
-      <c r="E12" s="5">
-        <v>7.99</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="5">
-        <v>26.4</v>
-      </c>
-      <c r="C13" s="5">
-        <v>5.5</v>
-      </c>
-      <c r="D13" s="5">
-        <v>36.729999999999997</v>
-      </c>
-      <c r="E13" s="5">
-        <v>7.99</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="5">
-        <v>29.1</v>
-      </c>
-      <c r="C14" s="5">
-        <v>6.25</v>
-      </c>
-      <c r="D14" s="5">
-        <v>37.369999999999997</v>
-      </c>
-      <c r="E14" s="5">
-        <v>7.83</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="5">
-        <v>21.8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>7.33</v>
-      </c>
-      <c r="D16" s="5">
-        <v>31.9</v>
-      </c>
-      <c r="E16" s="5">
-        <v>7.86</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="5">
-        <v>29.8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>4.92</v>
-      </c>
-      <c r="D17" s="5">
-        <v>37.54</v>
-      </c>
-      <c r="E17" s="5">
-        <v>7.78</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="5">
-        <v>27.6</v>
-      </c>
-      <c r="C18" s="5">
+      <c r="C43" s="13">
+        <v>3.61</v>
+      </c>
+      <c r="D43" s="13">
+        <v>35.74</v>
+      </c>
+      <c r="E43" s="13">
+        <v>7.79</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="13">
+        <v>30.4</v>
+      </c>
+      <c r="C44" s="13">
+        <v>3.66</v>
+      </c>
+      <c r="D44" s="13">
+        <v>37.39</v>
+      </c>
+      <c r="E44" s="13">
+        <v>7.91</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="13">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="C45" s="13">
         <v>5.41</v>
       </c>
-      <c r="D18" s="5">
-        <v>34.08</v>
-      </c>
-      <c r="E18" s="5">
-        <v>7.85</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" s="3"/>
+      <c r="D45" s="13">
+        <v>37.479999999999997</v>
+      </c>
+      <c r="E45" s="13">
+        <v>7.98</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="13">
+        <v>28.3</v>
+      </c>
+      <c r="C46" s="13">
+        <v>3.56</v>
+      </c>
+      <c r="D46" s="13">
+        <v>35.82</v>
+      </c>
+      <c r="E46" s="13">
+        <v>7.88</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="13">
+        <v>31.5</v>
+      </c>
+      <c r="C47" s="13">
+        <v>6.94</v>
+      </c>
+      <c r="D47" s="13">
+        <v>34.24</v>
+      </c>
+      <c r="E47" s="13">
+        <v>7.97</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="5"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>